--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BC32A4-5EA9-468E-A8F8-EF482A9636DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D34DB3E0D1C83D2766F3AC1671D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA978FE6-6F96-4F09-ACDE-179C841D194C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 14-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -689,9 +689,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -793,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -813,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -956,7 +956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>106</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D34DB3E0D1C83D2766F3AC1671D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA978FE6-6F96-4F09-ACDE-179C841D194C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D34DB3E0D1C83D606672AE2871D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23D800C-778A-4BAA-9389-D2A8905EB846}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D34DB3E0D1C83D606672AE2871D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23D800C-778A-4BAA-9389-D2A8905EB846}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833AD750-E29D-4777-BB7B-1FB0B408F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -689,9 +689,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -793,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -813,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -956,7 +956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>106</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833AD750-E29D-4777-BB7B-1FB0B408F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4497AB-600C-4080-8ED2-E0C2FE36BBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 14-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 17-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -58,7 +58,7 @@
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (Xmedicus Systems)</t>
+    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -689,9 +689,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -793,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -813,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -956,7 +956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>106</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4497AB-600C-4080-8ED2-E0C2FE36BBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD15AC96-4E6F-4072-8C3B-CB51A3894B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD15AC96-4E6F-4072-8C3B-CB51A3894B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96FBD73F321C93D9DF6B2AE9671D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC6BD0E5-0F84-4272-A1CF-1444C81DC2BA}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 17-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 18-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -689,9 +689,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -793,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -813,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -956,7 +956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>106</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96FBD73F321C93D9DF6B2AE9671D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC6BD0E5-0F84-4272-A1CF-1444C81DC2BA}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96FBD73F321C93DFDDEF4A91C70D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{878A04E5-64C2-45D9-84D5-F59169A505D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 18-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 21-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96FBD73F321C93DFDDEF4A91C70D85ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{878A04E5-64C2-45D9-84D5-F59169A505D9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793DCDA8-A5C7-4103-AFA9-3E08551AB6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -689,9 +689,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -793,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -813,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -956,7 +956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>106</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793DCDA8-A5C7-4103-AFA9-3E08551AB6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CBEEC2-041F-415A-B969-911AD73CBE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 21-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CBEEC2-041F-415A-B969-911AD73CBE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8969E7A4-E5A5-4D02-8D83-801AD309C296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8969E7A4-E5A5-4D02-8D83-801AD309C296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246798E-8F91-4900-8C0C-B3E480651E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-09-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="109">
   <si>
     <t>Standard</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Novax _LPS_ (Novax)</t>
+  </si>
+  <si>
+    <t>PraksisJournal (PraksisJournal)</t>
   </si>
   <si>
     <t>Vena (Vena)</t>
@@ -688,10 +691,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -731,1439 +734,1448 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
         <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
         <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
         <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
         <v>17</v>
       </c>
       <c r="M17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" t="s">
         <v>17</v>
       </c>
       <c r="M20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" t="s">
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="M26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
-      </c>
-      <c r="K27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="M28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>74</v>
       </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s">
-        <v>16</v>
-      </c>
-      <c r="K31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>84</v>
-      </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>96</v>
       </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M49" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246798E-8F91-4900-8C0C-B3E480651E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9F9357BAEBBAA2E592E739AC870D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CA563F-BBDB-42DA-82E5-0E620C56D956}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -692,9 +692,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -802,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -825,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -866,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -907,7 +907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -948,7 +948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -968,7 +968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -985,7 +985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -999,7 +999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1268,13 +1268,13 @@
         <v>17</v>
       </c>
       <c r="M17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>107</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9F9357BAEBBAA2E592E739AC870D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CA563F-BBDB-42DA-82E5-0E620C56D956}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD95FC988FAB2E187EF2B2FE71D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA01775E-F6A4-44F7-9C3F-00915589EFB1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-09-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 24-09-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
+    <t>XMedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -82,7 +82,7 @@
     <t>Tester</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD95FC988FAB2E187EF2B2FE71D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA01775E-F6A4-44F7-9C3F-00915589EFB1}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD95FC988FAB2E10EE32B64C71D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC566B21-9856-423B-A931-6501E013CF82}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD95FC988FAB2E10EE32B64C71D85B8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC566B21-9856-423B-A931-6501E013CF82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B87118-0417-4AEA-BE26-B2E631B6F07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 24-09-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 28-09-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -692,9 +692,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -802,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -825,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -866,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -907,7 +907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -948,7 +948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -968,7 +968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -985,7 +985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -999,7 +999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>107</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B87118-0417-4AEA-BE26-B2E631B6F07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E27D3EAA27AA2ECD26F4A6CE70D857CA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61FD3BC-D166-44FC-BE98-FBA9A43CBD94}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 28-09-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="109">
   <si>
     <t>Standard</t>
   </si>
@@ -692,9 +692,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -802,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -825,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -866,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -907,7 +907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -948,7 +948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -968,7 +968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -985,7 +985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -999,7 +999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1027,6 +1027,9 @@
       <c r="I11" t="s">
         <v>17</v>
       </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1065,6 +1068,9 @@
       <c r="I12" t="s">
         <v>17</v>
       </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
       <c r="K12" t="s">
         <v>17</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1106,6 +1112,9 @@
       <c r="I13" t="s">
         <v>17</v>
       </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
       <c r="K13" t="s">
         <v>17</v>
       </c>
@@ -1119,7 +1128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1147,6 +1156,9 @@
       <c r="I14" t="s">
         <v>17</v>
       </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
       <c r="K14" t="s">
         <v>17</v>
       </c>
@@ -1160,7 +1172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1188,6 +1200,9 @@
       <c r="I15" t="s">
         <v>17</v>
       </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
       <c r="K15" t="s">
         <v>17</v>
       </c>
@@ -1201,7 +1216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1233,7 +1248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1261,6 +1276,9 @@
       <c r="I17" t="s">
         <v>17</v>
       </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
       <c r="K17" t="s">
         <v>17</v>
       </c>
@@ -1274,7 +1292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1302,6 +1320,9 @@
       <c r="I18" t="s">
         <v>17</v>
       </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
       <c r="K18" t="s">
         <v>17</v>
       </c>
@@ -1315,7 +1336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1343,6 +1364,9 @@
       <c r="I19" t="s">
         <v>17</v>
       </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
       <c r="K19" t="s">
         <v>17</v>
       </c>
@@ -1356,7 +1380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1384,6 +1408,9 @@
       <c r="I20" t="s">
         <v>17</v>
       </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
       <c r="K20" t="s">
         <v>17</v>
       </c>
@@ -1397,7 +1424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1425,6 +1452,9 @@
       <c r="I21" t="s">
         <v>17</v>
       </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
       <c r="K21" t="s">
         <v>17</v>
       </c>
@@ -1438,7 +1468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1473,7 +1503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1511,7 +1541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1539,6 +1569,9 @@
       <c r="I24" t="s">
         <v>17</v>
       </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
       <c r="K24" t="s">
         <v>17</v>
       </c>
@@ -1549,7 +1582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1577,6 +1610,9 @@
       <c r="I25" t="s">
         <v>17</v>
       </c>
+      <c r="J25" t="s">
+        <v>18</v>
+      </c>
       <c r="K25" t="s">
         <v>17</v>
       </c>
@@ -1587,7 +1623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1601,7 +1637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1633,7 +1669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1647,7 +1683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1661,7 +1697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1693,7 +1729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1725,7 +1761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1757,7 +1793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1785,6 +1821,9 @@
       <c r="I33" t="s">
         <v>17</v>
       </c>
+      <c r="J33" t="s">
+        <v>18</v>
+      </c>
       <c r="K33" t="s">
         <v>17</v>
       </c>
@@ -1798,7 +1837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1830,7 +1869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1858,6 +1897,9 @@
       <c r="I35" t="s">
         <v>17</v>
       </c>
+      <c r="J35" t="s">
+        <v>18</v>
+      </c>
       <c r="K35" t="s">
         <v>17</v>
       </c>
@@ -1871,7 +1913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -1899,6 +1941,9 @@
       <c r="I36" t="s">
         <v>17</v>
       </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
       <c r="K36" t="s">
         <v>17</v>
       </c>
@@ -1912,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1926,7 +1971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1936,11 +1981,14 @@
       <c r="C38" t="s">
         <v>16</v>
       </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
       <c r="K38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1954,7 +2002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1968,7 +2016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1982,7 +2030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -1996,7 +2044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2021,6 +2069,9 @@
       <c r="I43" t="s">
         <v>17</v>
       </c>
+      <c r="J43" t="s">
+        <v>18</v>
+      </c>
       <c r="K43" t="s">
         <v>17</v>
       </c>
@@ -2031,7 +2082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2045,7 +2096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -2073,6 +2124,9 @@
       <c r="I45" t="s">
         <v>17</v>
       </c>
+      <c r="J45" t="s">
+        <v>18</v>
+      </c>
       <c r="K45" t="s">
         <v>17</v>
       </c>
@@ -2083,7 +2137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2109,7 +2163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -2123,7 +2177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -2137,7 +2191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>107</v>
       </c>
@@ -2164,6 +2218,9 @@
       </c>
       <c r="I49" t="s">
         <v>17</v>
+      </c>
+      <c r="J49" t="s">
+        <v>18</v>
       </c>
       <c r="K49" t="s">
         <v>17</v>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8969E7A4-E5A5-4D02-8D83-801AD309C296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEA662F-12F9-4563-AE44-028F6A7B54AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="109">
   <si>
     <t>Standard</t>
   </si>
@@ -52,13 +52,16 @@
     <t>Novax _LPS_ (Novax)</t>
   </si>
   <si>
+    <t>PraksisJournal (PraksisJournal)</t>
+  </si>
+  <si>
     <t>Vena (Vena)</t>
   </si>
   <si>
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
+    <t>XMedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -79,7 +82,7 @@
     <t>Tester</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>
@@ -688,10 +691,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -731,1439 +734,1505 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
         <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
         <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
         <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
         <v>17</v>
       </c>
       <c r="M17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" t="s">
         <v>17</v>
       </c>
       <c r="M20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" t="s">
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="M26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
-      </c>
-      <c r="K27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="M28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>74</v>
       </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s">
-        <v>16</v>
-      </c>
-      <c r="K31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>84</v>
-      </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>96</v>
       </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M49" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E27D3EAA27AA2ECD26F4A6CE70D857CA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61FD3BC-D166-44FC-BE98-FBA9A43CBD94}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67608E47-8C2C-40F0-86C0-629396283B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-10-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -692,9 +692,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -802,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -825,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -866,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -907,7 +907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -948,7 +948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -968,7 +968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -985,7 +985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -999,7 +999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>107</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67608E47-8C2C-40F0-86C0-629396283B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E27D3EAA27AA2EE82675B06270D857D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F05C2DE7-C2C5-4666-A630-11CF39A5A3A6}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 07-10-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 08-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E27D3EAA27AA2EE82675B06270D857D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F05C2DE7-C2C5-4666-A630-11CF39A5A3A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679ECF87-0B9B-46F2-9C04-4AFC20327D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 08-10-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679ECF87-0B9B-46F2-9C04-4AFC20327D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA063639-E657-4D83-8FDE-FB660455BEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA063639-E657-4D83-8FDE-FB660455BEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E27D3EAA27AA2EBC76729C5470D857D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{656A9A6E-8DB4-410B-AEA7-A69FF433B98E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-10-2026'!$A$1:$N$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-10-2026'!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
